--- a/KURIKULUM2026_REVISI/035_RESTRUKTURISASI_KODE_MK_PEMINATAN_STA_STB_STC.xlsx
+++ b/KURIKULUM2026_REVISI/035_RESTRUKTURISASI_KODE_MK_PEMINATAN_STA_STB_STC.xlsx
@@ -1050,7 +1050,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>`STI-413` Machine Learning, `STI-624` Integrasi AI</t>
+          <t>`STI-413` Machine Learning, `STI-726` Integrasi AI</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>`STI-626` Deep Learning, `STI-521` IoT</t>
+          <t>`STI-726` Deep Learning, `STI-521` IoT</t>
         </is>
       </c>
     </row>
